--- a/Questions - Round 2.xlsx
+++ b/Questions - Round 2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cafnzholding-my.sharepoint.com/personal/thom_van_dusschoten_synerlogic_nl/Documents/Documenten/GitHub/Sustainability-quiz/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="34" documentId="13_ncr:1_{6B9D40C8-13C7-40B1-9849-545052FB2826}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7254AC0F-27B2-474E-8FC8-95BBE3EEAA21}"/>
+  <xr:revisionPtr revIDLastSave="36" documentId="13_ncr:1_{6B9D40C8-13C7-40B1-9849-545052FB2826}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{15D26AFE-C262-4916-8B00-B169BE6A6A18}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EN" sheetId="1" r:id="rId1"/>
@@ -192,7 +192,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="76">
   <si>
     <t>type</t>
   </si>
@@ -224,9 +224,6 @@
     <t>single</t>
   </si>
   <si>
-    <t>What does sustainability in everyday work mean most of all?</t>
-  </si>
-  <si>
     <t>Single choice</t>
   </si>
   <si>
@@ -251,9 +248,6 @@
     <t>multiple</t>
   </si>
   <si>
-    <t>Which goals fit the “Zero in Focus” idea?</t>
-  </si>
-  <si>
     <t>Multiple choice</t>
   </si>
   <si>
@@ -423,6 +417,9 @@
   </si>
   <si>
     <t>Le concept « Zero in Focus » combine les objectifs liés au climat, à la sécurité et à l’intégrité. La formation n’est pas un objectif du programme « Zero ».</t>
+  </si>
+  <si>
+    <t>TEST</t>
   </si>
 </sst>
 </file>
@@ -943,57 +940,57 @@
         <v>9</v>
       </c>
       <c r="B2" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="D2" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="E2" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="F2" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="G2" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="H2" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="I2" s="2" t="s">
         <v>16</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="D3" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="E3" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="F3" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="G3" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="H3" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="I3" s="2" t="s">
         <v>24</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>26</v>
       </c>
     </row>
   </sheetData>
@@ -1052,57 +1049,57 @@
         <v>9</v>
       </c>
       <c r="B2" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D2" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="E2" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="F2" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="G2" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="H2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I2" s="2" t="s">
         <v>31</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B3" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D3" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="E3" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="F3" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="G3" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="H3" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I3" s="2" t="s">
         <v>38</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
@@ -1172,57 +1169,57 @@
         <v>9</v>
       </c>
       <c r="B2" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D2" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="E2" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="F2" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="G2" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="H2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I2" s="2" t="s">
         <v>45</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B3" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="D3" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="E3" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="F3" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="G3" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="H3" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I3" s="2" t="s">
         <v>74</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>76</v>
       </c>
     </row>
   </sheetData>
@@ -1281,57 +1278,57 @@
         <v>9</v>
       </c>
       <c r="B2" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D2" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="E2" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="F2" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="G2" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="H2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I2" s="2" t="s">
         <v>52</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B3" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="D3" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="E3" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="F3" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="G3" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="H3" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I3" s="2" t="s">
         <v>59</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>61</v>
       </c>
     </row>
   </sheetData>
@@ -1353,7 +1350,7 @@
   <sheetData>
     <row r="1" spans="1:1" ht="21" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
@@ -1361,32 +1358,32 @@
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
@@ -1394,7 +1391,7 @@
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
   </sheetData>

--- a/Questions - Round 2.xlsx
+++ b/Questions - Round 2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cafnzholding-my.sharepoint.com/personal/thom_van_dusschoten_synerlogic_nl/Documents/Documenten/GitHub/Sustainability-quiz/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="36" documentId="13_ncr:1_{6B9D40C8-13C7-40B1-9849-545052FB2826}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{15D26AFE-C262-4916-8B00-B169BE6A6A18}"/>
+  <xr:revisionPtr revIDLastSave="40" documentId="13_ncr:1_{6B9D40C8-13C7-40B1-9849-545052FB2826}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0669CFBE-5DF3-4AEB-956F-786C47492769}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EN" sheetId="1" r:id="rId1"/>
@@ -192,7 +192,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="77">
   <si>
     <t>type</t>
   </si>
@@ -419,7 +419,10 @@
     <t>Le concept « Zero in Focus » combine les objectifs liés au climat, à la sécurité et à l’intégrité. La formation n’est pas un objectif du programme « Zero ».</t>
   </si>
   <si>
-    <t>TEST</t>
+    <t>(Round 2) What does sustainability in everyday work mean most of all?</t>
+  </si>
+  <si>
+    <t>(Round 2) Which goals fit the “Zero in Focus” idea?</t>
   </si>
 </sst>
 </file>
@@ -969,7 +972,7 @@
         <v>17</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>18</v>

--- a/Questions - Round 2.xlsx
+++ b/Questions - Round 2.xlsx
@@ -1,16 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30327"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cafnzholding-my.sharepoint.com/personal/thom_van_dusschoten_synerlogic_nl/Documents/Documenten/GitHub/Sustainability-quiz/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="40" documentId="13_ncr:1_{6B9D40C8-13C7-40B1-9849-545052FB2826}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0669CFBE-5DF3-4AEB-956F-786C47492769}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{5C179905-64A5-414E-AD2C-881CA5C244FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EN" sheetId="1" r:id="rId1"/>
@@ -43,6 +38,7 @@
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>Microsoft Copilot</author>
+    <author>Copilot</author>
   </authors>
   <commentList>
     <comment ref="A1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
@@ -73,6 +69,20 @@
         </r>
       </text>
     </comment>
+    <comment ref="I1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Sources: STOCKMEIER Group Sustainability Report 2024/2025; https://sdgs.un.org/goals/goal13; https://sdgs.un.org/goals/goal13#targets_and_indicators; https://www.nationalgeographic.nl/226-manieren-om-onze-voetafdruk-te-verkleinen; https://www.wwf.nl/kom-in-actie/voetafdruktest; https://www.wwf.nl/work-in-progress/kom-in-actie/met-tijd/tips-gedrag/reizen</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
@@ -81,6 +91,7 @@
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>Microsoft Copilot</author>
+    <author>Copilot</author>
   </authors>
   <commentList>
     <comment ref="A1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000001000000}">
@@ -111,6 +122,20 @@
         </r>
       </text>
     </comment>
+    <comment ref="I1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0100-000003000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Sources: STOCKMEIER Group Sustainability Report 2024/2025; https://sdgs.un.org/goals/goal13; https://sdgs.un.org/goals/goal13#targets_and_indicators; https://www.nationalgeographic.nl/226-manieren-om-onze-voetafdruk-te-verkleinen; https://www.wwf.nl/kom-in-actie/voetafdruktest; https://www.wwf.nl/work-in-progress/kom-in-actie/met-tijd/tips-gedrag/reizen</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
@@ -119,6 +144,7 @@
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>Microsoft Copilot</author>
+    <author>Copilot</author>
   </authors>
   <commentList>
     <comment ref="A1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000001000000}">
@@ -149,6 +175,20 @@
         </r>
       </text>
     </comment>
+    <comment ref="I1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0200-000003000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Sources: STOCKMEIER Group Sustainability Report 2024/2025; https://sdgs.un.org/goals/goal13; https://sdgs.un.org/goals/goal13#targets_and_indicators; https://www.nationalgeographic.nl/226-manieren-om-onze-voetafdruk-te-verkleinen; https://www.wwf.nl/kom-in-actie/voetafdruktest; https://www.wwf.nl/work-in-progress/kom-in-actie/met-tijd/tips-gedrag/reizen</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
@@ -157,6 +197,7 @@
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>Microsoft Copilot</author>
+    <author>Copilot</author>
   </authors>
   <commentList>
     <comment ref="A1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000001000000}">
@@ -187,12 +228,26 @@
         </r>
       </text>
     </comment>
+    <comment ref="I1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0300-000003000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Sources: STOCKMEIER Group Sustainability Report 2024/2025; https://sdgs.un.org/goals/goal13; https://sdgs.un.org/goals/goal13#targets_and_indicators; https://www.nationalgeographic.nl/226-manieren-om-onze-voetafdruk-te-verkleinen; https://www.wwf.nl/kom-in-actie/voetafdruktest; https://www.wwf.nl/work-in-progress/kom-in-actie/met-tijd/tips-gedrag/reizen</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="477" uniqueCount="309">
   <si>
     <t>type</t>
   </si>
@@ -224,169 +279,892 @@
     <t>single</t>
   </si>
   <si>
+    <t>SDG 13 is called Climate Action. What is the main idea behind this goal?</t>
+  </si>
+  <si>
     <t>Single choice</t>
   </si>
   <si>
-    <t>Only large projects matter, not small daily decisions.</t>
-  </si>
-  <si>
-    <t>Sustainability is an ongoing process that we can support every day.</t>
-  </si>
-  <si>
-    <t>Sustainability only concerns environmental departments and managers.</t>
-  </si>
-  <si>
-    <t>Sustainability is a topic for later, not for today's work.</t>
+    <t>Planting more trees is the only climate solution.</t>
+  </si>
+  <si>
+    <t>Taking urgent action to combat climate change and its impacts.</t>
+  </si>
+  <si>
+    <t>Waiting until climate change becomes easier to measure.</t>
+  </si>
+  <si>
+    <t>Only governments need to act; companies and people do not matter.</t>
   </si>
   <si>
     <t>1</t>
   </si>
   <si>
-    <t>The report describes sustainability as a daily path, not a one-time goal.</t>
+    <t>Correct: SDG 13 is about urgent action against climate change and its impacts. STOCKMEIER links this to emission tracking, climate risk management and decarbonization. You can help by choosing lower-emission habits at work and at home.</t>
   </si>
   <si>
     <t>multiple</t>
   </si>
   <si>
+    <t>Which three topics are part of the SDG 13 targets?</t>
+  </si>
+  <si>
     <t>Multiple choice</t>
   </si>
   <si>
-    <t>Zero CO₂ emissions</t>
-  </si>
-  <si>
-    <t>Zero accidents at work</t>
-  </si>
-  <si>
-    <t>Zero tolerance for unethical behaviour</t>
-  </si>
-  <si>
-    <t>Zero training</t>
+    <t>Strengthening resilience to climate-related hazards.</t>
+  </si>
+  <si>
+    <t>Integrating climate measures into policies and planning.</t>
+  </si>
+  <si>
+    <t>Improving climate education and awareness.</t>
+  </si>
+  <si>
+    <t>Making every country use exactly the same climate policy.</t>
   </si>
   <si>
     <t>0,1,2</t>
   </si>
   <si>
-    <t>The idea combines climate, safety and integrity. Training is not a “Zero” goal.</t>
-  </si>
-  <si>
-    <t>Wat betekent duurzaamheid in het dagelijkse werk vooral?</t>
+    <t>Correct answers: resilience, policy integration and education. SDG 13 does not say every country must use one identical policy. STOCKMEIER supports this by identifying climate risks and building internal sustainability knowledge. You can help by learning and sharing practical climate actions.</t>
+  </si>
+  <si>
+    <t>Why does SDG 13 talk about “resilience” and not only about “reducing emissions”?</t>
+  </si>
+  <si>
+    <t>Because reducing emissions is no longer useful.</t>
+  </si>
+  <si>
+    <t>Because climate risks only affect coastal countries.</t>
+  </si>
+  <si>
+    <t>Because societies also need to prepare for floods, heatwaves and other climate impacts.</t>
+  </si>
+  <si>
+    <t>Because resilience means ignoring climate change.</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>Correct: SDG 13 includes adaptation to climate-related hazards. STOCKMEIER recognizes risks such as floods, heatwaves and logistics disruption. You can help by following safety and emergency procedures and reporting improvement ideas.</t>
+  </si>
+  <si>
+    <t>Which greenhouse gas accounting scopes are normally used to understand a company’s climate footprint?</t>
+  </si>
+  <si>
+    <t>Scope 1, Scope 2 and Scope 3.</t>
+  </si>
+  <si>
+    <t>Scope A, Scope B and Scope C.</t>
+  </si>
+  <si>
+    <t>Only electricity use.</t>
+  </si>
+  <si>
+    <t>Only emissions from office printers.</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>Correct: companies commonly use Scope 1, 2 and 3. STOCKMEIER completed CO2 accounting for the Group using the GHG Protocol, including significant upstream and downstream Scope 3 emissions. You can help by reducing waste, energy use and unnecessary transport.</t>
+  </si>
+  <si>
+    <t>STOCKMEIER has a “Zero Carbon” ambition. By which year does the report say the Group aspires to zero carbon emissions?</t>
+  </si>
+  <si>
+    <t>2028</t>
+  </si>
+  <si>
+    <t>2030</t>
+  </si>
+  <si>
+    <t>2032</t>
+  </si>
+  <si>
+    <t>2035</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>Correct: the report states an aspiration for zero carbon emissions by 2035. That supports SDG 13 by setting a clear long-term climate direction. You can help by making daily work more energy- and resource-efficient.</t>
+  </si>
+  <si>
+    <t>Which actions from the STOCKMEIER report directly support climate action?</t>
+  </si>
+  <si>
+    <t>GHG accounting for Scope 1, 2 and 3.</t>
+  </si>
+  <si>
+    <t>Expanding photovoltaic energy at STOCKMEIER Quimica.</t>
+  </si>
+  <si>
+    <t>Promoting e-mobility in the company fleet.</t>
+  </si>
+  <si>
+    <t>Stopping all sustainability reporting because it creates paperwork.</t>
+  </si>
+  <si>
+    <t>Correct: GHG accounting, PV energy and e-mobility all support climate action. Reporting is used for transparency and improvement, not something to stop. You can help by using data, reporting issues and choosing efficient travel when possible.</t>
+  </si>
+  <si>
+    <t>What is the difference between climate mitigation and climate adaptation?</t>
+  </si>
+  <si>
+    <t>Mitigation is only for companies; adaptation is only for households.</t>
+  </si>
+  <si>
+    <t>Mitigation reduces the causes of climate change; adaptation prepares for the impacts.</t>
+  </si>
+  <si>
+    <t>Mitigation means emergency response after a flood; adaptation means producing more CO2.</t>
+  </si>
+  <si>
+    <t>There is no difference.</t>
+  </si>
+  <si>
+    <t>Correct: mitigation tackles causes, adaptation prepares for impacts. STOCKMEIER works on both through decarbonization and climate risk analysis. You can help by reducing emissions and staying prepared for extreme weather procedures.</t>
+  </si>
+  <si>
+    <t>Why is climate education part of SDG 13?</t>
+  </si>
+  <si>
+    <t>Because knowledge alone automatically solves climate change.</t>
+  </si>
+  <si>
+    <t>Because only students need to understand climate change.</t>
+  </si>
+  <si>
+    <t>Because people make better decisions when they understand causes, impacts and solutions.</t>
+  </si>
+  <si>
+    <t>Because climate education replaces practical action.</t>
+  </si>
+  <si>
+    <t>Correct: education helps people make better decisions. STOCKMEIER includes sustainability training and awareness as part of its practices. You can help by asking questions, sharing ideas and turning knowledge into action.</t>
+  </si>
+  <si>
+    <t>What climate-related risk does the STOCKMEIER report explicitly mention for operations and supply chains?</t>
+  </si>
+  <si>
+    <t>Floods, heatwaves and disrupted logistics can affect production, storage and transport.</t>
+  </si>
+  <si>
+    <t>Only too many trees around a site.</t>
+  </si>
+  <si>
+    <t>Only a shortage of office chairs.</t>
+  </si>
+  <si>
+    <t>Climate risks exist only far away from Europe.</t>
+  </si>
+  <si>
+    <t>Correct: the report mentions floods, extreme heat and logistics disruptions as climate risks. STOCKMEIER plans further site-specific climate risk analysis before 2030. You can help by taking weather warnings and site procedures seriously.</t>
+  </si>
+  <si>
+    <t>Which everyday choice most clearly reduces your personal climate footprint?</t>
+  </si>
+  <si>
+    <t>Buying more products because newer is always greener.</t>
+  </si>
+  <si>
+    <t>Leaving heating, lights and equipment on because one person makes no difference.</t>
+  </si>
+  <si>
+    <t>Flying more often but recycling the boarding pass.</t>
+  </si>
+  <si>
+    <t>Using less energy, wasting less, choosing lower-impact transport and buying only what you need.</t>
+  </si>
+  <si>
+    <t>Correct: everyday choices in energy, transport, waste and consumption reduce footprint. STOCKMEIER works on efficiency and emissions, and you can mirror that mindset in daily choices at work and home.</t>
+  </si>
+  <si>
+    <t>What is one expected benefit of the photovoltaic project at STOCKMEIER Quimica’s L’Andana facility?</t>
+  </si>
+  <si>
+    <t>It will make climate reporting unnecessary.</t>
+  </si>
+  <si>
+    <t>It will generate renewable electricity and reduce reliance on grid electricity.</t>
+  </si>
+  <si>
+    <t>It will remove all Scope 3 emissions immediately.</t>
+  </si>
+  <si>
+    <t>It is mainly a decoration for warehouse roofs.</t>
+  </si>
+  <si>
+    <t>Correct: the PV project is expected to generate renewable electricity and reduce reliance on grid electricity. This supports the Zero Carbon direction. You can help by avoiding unnecessary electricity use so renewable energy goes further.</t>
+  </si>
+  <si>
+    <t>A climate plan becomes strongest when it combines which three ingredients?</t>
+  </si>
+  <si>
+    <t>Measurement, practical actions and learning.</t>
+  </si>
+  <si>
+    <t>Good intentions, posters and no follow-up.</t>
+  </si>
+  <si>
+    <t>Only one big project and no daily habits.</t>
+  </si>
+  <si>
+    <t>Waiting for someone else to start.</t>
+  </si>
+  <si>
+    <t>Correct: climate action needs measurement, practical actions and learning. STOCKMEIER combines GHG accounting, decarbonization projects, climate risk work and sustainability organization. You can help by turning awareness into small, repeatable actions.</t>
+  </si>
+  <si>
+    <t>SDG 13 heet Klimaatactie. Wat is de kern van dit doel?</t>
   </si>
   <si>
     <t>Enkelvoudige keuze</t>
   </si>
   <si>
-    <t>Alleen grote projecten tellen, niet kleine dagelijkse beslissingen.</t>
-  </si>
-  <si>
-    <t>Duurzaamheid is een doorlopend proces dat we elke dag kunnen ondersteunen.</t>
-  </si>
-  <si>
-    <t>Duurzaamheid gaat alleen over milieuafdelingen en managers.</t>
-  </si>
-  <si>
-    <t>Duurzaamheid is iets voor later, niet voor het werk van vandaag.</t>
-  </si>
-  <si>
-    <t>Het rapport beschrijft duurzaamheid als een dagelijkse route en niet als een eenmalig doel.</t>
-  </si>
-  <si>
-    <t>Welke doelen passen bij het idee “Zero in Focus”?</t>
+    <t>Meer bomen planten is de enige klimaatoplossing.</t>
+  </si>
+  <si>
+    <t>Dringend actie ondernemen tegen klimaatverandering en de gevolgen ervan.</t>
+  </si>
+  <si>
+    <t>Wachten tot klimaatverandering gemakkelijker te meten is.</t>
+  </si>
+  <si>
+    <t>Alleen overheden hoeven iets te doen; bedrijven en mensen tellen niet mee.</t>
+  </si>
+  <si>
+    <t>Correct: SDG 13 gaat over directe actie tegen klimaatverandering en de gevolgen ervan. STOCKMEIER koppelt dit aan emissiemetingen, klimaatrisico’s en decarbonisatie. Jij helpt door op werk en thuis keuzes met minder uitstoot te maken.</t>
+  </si>
+  <si>
+    <t>Welke drie onderwerpen horen bij de SDG 13-doelstellingen?</t>
   </si>
   <si>
     <t>Meerkeuze</t>
   </si>
   <si>
-    <t>Nul CO₂-uitstoot</t>
-  </si>
-  <si>
-    <t>Nul ongevallen op het werk</t>
-  </si>
-  <si>
-    <t>Nultolerantie voor onethisch gedrag</t>
-  </si>
-  <si>
-    <t>Nul training</t>
-  </si>
-  <si>
-    <t>Het idee combineert klimaat, veiligheid en integriteit. Training is geen “Zero”-doel.</t>
-  </si>
-  <si>
-    <t>Que signifie surtout la durabilité dans le travail quotidien ?</t>
+    <t>Weerbaarheid tegen klimaatgerelateerde risico’s versterken.</t>
+  </si>
+  <si>
+    <t>Klimaatmaatregelen opnemen in beleid en planning.</t>
+  </si>
+  <si>
+    <t>Klimaateducatie en bewustwording verbeteren.</t>
+  </si>
+  <si>
+    <t>Elk land exact hetzelfde klimaatbeleid laten gebruiken.</t>
+  </si>
+  <si>
+    <t>Correct: weerbaarheid, beleidsintegratie en educatie. SDG 13 verplicht landen niet tot exact hetzelfde beleid. STOCKMEIER werkt hieraan via klimaatrisico’s en interne duurzaamheidskennis. Jij helpt door te leren en praktische klimaatacties te delen.</t>
+  </si>
+  <si>
+    <t>Waarom spreekt SDG 13 over “weerbaarheid” en niet alleen over “uitstoot verminderen”?</t>
+  </si>
+  <si>
+    <t>Omdat uitstoot verminderen niet meer nuttig is.</t>
+  </si>
+  <si>
+    <t>Omdat klimaatrisico’s alleen kustlanden raken.</t>
+  </si>
+  <si>
+    <t>Omdat samenlevingen zich ook moeten voorbereiden op overstromingen, hittegolven en andere klimaatimpact.</t>
+  </si>
+  <si>
+    <t>Omdat weerbaarheid betekent dat je klimaatverandering negeert.</t>
+  </si>
+  <si>
+    <t>Correct: SDG 13 gaat ook over aanpassing aan klimaatrisico’s. STOCKMEIER benoemt risico’s zoals overstromingen, hittegolven en logistieke verstoringen. Jij helpt door veiligheids- en noodprocedures te volgen en verbeterideeën te melden.</t>
+  </si>
+  <si>
+    <t>Welke scopes worden normaal gebruikt om de klimaatvoetafdruk van een bedrijf te begrijpen?</t>
+  </si>
+  <si>
+    <t>Scope 1, Scope 2 en Scope 3.</t>
+  </si>
+  <si>
+    <t>Scope A, Scope B en Scope C.</t>
+  </si>
+  <si>
+    <t>Alleen elektriciteitsverbruik.</t>
+  </si>
+  <si>
+    <t>Alleen uitstoot van kantoorprinters.</t>
+  </si>
+  <si>
+    <t>Correct: bedrijven gebruiken meestal Scope 1, 2 en 3. STOCKMEIER heeft CO2-accounting voor de Groep uitgevoerd volgens het GHG Protocol, inclusief belangrijke Scope 3-uitstoot. Jij helpt door minder afval, energieverbruik en onnodig transport.</t>
+  </si>
+  <si>
+    <t>STOCKMEIER heeft een “Zero Carbon”-ambitie. In welk jaar wil de Groep volgens het rapport naar nul CO2-uitstoot?</t>
+  </si>
+  <si>
+    <t>Correct: het rapport noemt de ambitie van nul CO2-uitstoot in 2035. Dit ondersteunt SDG 13 met een duidelijke langetermijnrichting. Jij helpt door dagelijks energie en grondstoffen efficiënter te gebruiken.</t>
+  </si>
+  <si>
+    <t>Welke acties uit het STOCKMEIER-rapport ondersteunen klimaatactie direct?</t>
+  </si>
+  <si>
+    <t>GHG-accounting voor Scope 1, 2 en 3.</t>
+  </si>
+  <si>
+    <t>Uitbreiding van fotovoltaïsche energie bij STOCKMEIER Quimica.</t>
+  </si>
+  <si>
+    <t>Stimuleren van e-mobility in het wagenpark.</t>
+  </si>
+  <si>
+    <t>Stoppen met duurzaamheidsrapportage omdat het papierwerk is.</t>
+  </si>
+  <si>
+    <t>Correct: GHG-accounting, zonne-energie en e-mobility ondersteunen klimaatactie. Rapportage helpt juist bij transparantie en verbetering. Jij helpt door data goed te gebruiken, issues te melden en efficiënt te reizen waar mogelijk.</t>
+  </si>
+  <si>
+    <t>Wat is het verschil tussen klimaatmitigatie en klimaatadaptatie?</t>
+  </si>
+  <si>
+    <t>Mitigatie is alleen voor bedrijven; adaptatie alleen voor huishoudens.</t>
+  </si>
+  <si>
+    <t>Mitigatie vermindert de oorzaken van klimaatverandering; adaptatie bereidt voor op de gevolgen.</t>
+  </si>
+  <si>
+    <t>Mitigatie betekent noodhulp na een overstroming; adaptatie betekent meer CO2 produceren.</t>
+  </si>
+  <si>
+    <t>Er is geen verschil.</t>
+  </si>
+  <si>
+    <t>Correct: mitigatie pakt oorzaken aan, adaptatie bereidt voor op gevolgen. STOCKMEIER werkt aan beide via decarbonisatie en klimaatrisicoanalyse. Jij helpt door uitstoot te verminderen en voorbereid te zijn op extreem weer.</t>
+  </si>
+  <si>
+    <t>Waarom hoort klimaateducatie bij SDG 13?</t>
+  </si>
+  <si>
+    <t>Omdat kennis alleen klimaatverandering automatisch oplost.</t>
+  </si>
+  <si>
+    <t>Omdat alleen studenten klimaatverandering moeten begrijpen.</t>
+  </si>
+  <si>
+    <t>Omdat mensen betere keuzes maken als ze oorzaken, gevolgen en oplossingen begrijpen.</t>
+  </si>
+  <si>
+    <t>Omdat klimaateducatie praktische actie vervangt.</t>
+  </si>
+  <si>
+    <t>Correct: educatie helpt mensen betere keuzes te maken. STOCKMEIER noemt duurzaamheidstraining en bewustwording als onderdeel van de aanpak. Jij helpt door vragen te stellen, ideeën te delen en kennis om te zetten in actie.</t>
+  </si>
+  <si>
+    <t>Welk klimaatgerelateerd risico noemt het STOCKMEIER-rapport expliciet voor operatie en supply chain?</t>
+  </si>
+  <si>
+    <t>Overstromingen, hittegolven en logistieke verstoringen kunnen productie, opslag en transport raken.</t>
+  </si>
+  <si>
+    <t>Alleen te veel bomen rondom een locatie.</t>
+  </si>
+  <si>
+    <t>Alleen een tekort aan bureaustoelen.</t>
+  </si>
+  <si>
+    <t>Klimaatrisico’s bestaan alleen ver weg van Europa.</t>
+  </si>
+  <si>
+    <t>Correct: het rapport noemt overstromingen, extreme hitte en logistieke verstoringen. STOCKMEIER plant verdere locatiespecifieke klimaatrisicoanalyse vóór 2030. Jij helpt door weerswaarschuwingen en locatieprocedures serieus te nemen.</t>
+  </si>
+  <si>
+    <t>Welke dagelijkse keuze verlaagt je persoonlijke klimaatvoetafdruk het duidelijkst?</t>
+  </si>
+  <si>
+    <t>Meer producten kopen omdat nieuw altijd groener is.</t>
+  </si>
+  <si>
+    <t>Verwarming, lampen en apparatuur aan laten staan omdat één persoon geen verschil maakt.</t>
+  </si>
+  <si>
+    <t>Vaker vliegen maar je instapkaart recyclen.</t>
+  </si>
+  <si>
+    <t>Minder energie gebruiken, minder verspillen, kiezen voor vervoer met lagere impact en alleen kopen wat je nodig hebt.</t>
+  </si>
+  <si>
+    <t>Correct: keuzes rond energie, vervoer, afval en consumptie verlagen je voetafdruk. STOCKMEIER werkt aan efficiëntie en emissiereductie; jij kunt dezelfde manier van denken toepassen op werk en thuis.</t>
+  </si>
+  <si>
+    <t>Wat is een verwacht voordeel van het fotovoltaïsche project bij STOCKMEIER Quimica in L’Andana?</t>
+  </si>
+  <si>
+    <t>Het maakt klimaatrapportage overbodig.</t>
+  </si>
+  <si>
+    <t>Het wekt hernieuwbare elektriciteit op en vermindert afhankelijkheid van netstroom.</t>
+  </si>
+  <si>
+    <t>Het verwijdert direct alle Scope 3-uitstoot.</t>
+  </si>
+  <si>
+    <t>Het is vooral decoratie voor magazijndaken.</t>
+  </si>
+  <si>
+    <t>Correct: het PV-project moet hernieuwbare elektriciteit opwekken en afhankelijkheid van netstroom verlagen. Dat ondersteunt Zero Carbon. Jij helpt door onnodig stroomverbruik te vermijden.</t>
+  </si>
+  <si>
+    <t>Een klimaatplan wordt het sterkst wanneer het welke drie onderdelen combineert?</t>
+  </si>
+  <si>
+    <t>Meten, praktische acties en leren.</t>
+  </si>
+  <si>
+    <t>Goede bedoelingen, posters en geen opvolging.</t>
+  </si>
+  <si>
+    <t>Alleen één groot project en geen dagelijkse gewoontes.</t>
+  </si>
+  <si>
+    <t>Wachten tot iemand anders begint.</t>
+  </si>
+  <si>
+    <t>Correct: klimaatactie vraagt om meten, praktische acties en leren. STOCKMEIER combineert GHG-accounting, decarbonisatieprojecten, klimaatrisico’s en een duurzaamheidsorganisatie. Jij helpt door bewustwording om te zetten in kleine, herhaalbare acties.</t>
+  </si>
+  <si>
+    <t>L’ODD 13 s’appelle Mesures relatives à la lutte contre les changements climatiques. Quelle est son idée principale ?</t>
   </si>
   <si>
     <t>Choix unique</t>
   </si>
   <si>
-    <t>Seuls les grands projets comptent, pas les petites décisions quotidiennes.</t>
-  </si>
-  <si>
-    <t>La durabilité est un processus continu que nous pouvons soutenir chaque jour.</t>
-  </si>
-  <si>
-    <t>La durabilité ne concerne que les services environnement et les managers.</t>
-  </si>
-  <si>
-    <t>La durabilité est un sujet pour plus tard, pas pour le travail d’aujourd’hui.</t>
-  </si>
-  <si>
-    <t>Le rapport décrit la durabilité comme une démarche quotidienne, pas comme un objectif ponctuel.</t>
-  </si>
-  <si>
-    <t>Was bedeutet Nachhaltigkeit im Arbeitsalltag vor allem?</t>
+    <t>Planter plus d’arbres est la seule solution climatique.</t>
+  </si>
+  <si>
+    <t>Prendre d’urgence des mesures pour lutter contre les changements climatiques et leurs impacts.</t>
+  </si>
+  <si>
+    <t>Attendre que le changement climatique soit plus facile à mesurer.</t>
+  </si>
+  <si>
+    <t>Seuls les gouvernements doivent agir ; les entreprises et les personnes ne comptent pas.</t>
+  </si>
+  <si>
+    <t>Correct : l’ODD 13 vise une action urgente contre le changement climatique et ses impacts. STOCKMEIER le relie au suivi des émissions, aux risques climatiques et à la décarbonation. Chacun peut aider par des choix à plus faibles émissions.</t>
+  </si>
+  <si>
+    <t>Quels trois thèmes font partie des cibles de l’ODD 13 ?</t>
+  </si>
+  <si>
+    <t>Choix multiples</t>
+  </si>
+  <si>
+    <t>Renforcer la résilience face aux risques climatiques.</t>
+  </si>
+  <si>
+    <t>Intégrer les mesures climatiques dans les politiques et la planification.</t>
+  </si>
+  <si>
+    <t>Améliorer l’éducation et la sensibilisation au climat.</t>
+  </si>
+  <si>
+    <t>Faire appliquer exactement la même politique climatique à tous les pays.</t>
+  </si>
+  <si>
+    <t>Correct : résilience, intégration dans les politiques et éducation. L’ODD 13 n’impose pas une politique identique partout. STOCKMEIER agit par l’analyse des risques climatiques et la formation interne. Chacun peut apprendre et partager des actions concrètes.</t>
+  </si>
+  <si>
+    <t>Pourquoi l’ODD 13 parle-t-il de « résilience » et pas seulement de « réduction des émissions » ?</t>
+  </si>
+  <si>
+    <t>Parce que réduire les émissions n’est plus utile.</t>
+  </si>
+  <si>
+    <t>Parce que les risques climatiques ne touchent que les pays côtiers.</t>
+  </si>
+  <si>
+    <t>Parce que les sociétés doivent aussi se préparer aux inondations, vagues de chaleur et autres impacts climatiques.</t>
+  </si>
+  <si>
+    <t>Parce que résilience signifie ignorer le changement climatique.</t>
+  </si>
+  <si>
+    <t>Correct : l’ODD 13 inclut l’adaptation aux risques climatiques. STOCKMEIER identifie des risques comme les inondations, les vagues de chaleur et les perturbations logistiques. Chacun peut aider en respectant les procédures de sécurité et en proposant des améliorations.</t>
+  </si>
+  <si>
+    <t>Quels scopes sont normalement utilisés pour comprendre l’empreinte climatique d’une entreprise ?</t>
+  </si>
+  <si>
+    <t>Scope 1, Scope 2 et Scope 3.</t>
+  </si>
+  <si>
+    <t>Scope A, Scope B et Scope C.</t>
+  </si>
+  <si>
+    <t>Uniquement la consommation d’électricité.</t>
+  </si>
+  <si>
+    <t>Uniquement les émissions des imprimantes de bureau.</t>
+  </si>
+  <si>
+    <t>Correct : les entreprises utilisent généralement les scopes 1, 2 et 3. STOCKMEIER a réalisé une comptabilité CO2 du Groupe selon le GHG Protocol, y compris les émissions significatives de Scope 3. Chacun peut réduire les déchets, l’énergie et les transports inutiles.</t>
+  </si>
+  <si>
+    <t>STOCKMEIER a une ambition « Zero Carbon ». Selon le rapport, pour quelle année le Groupe vise-t-il zéro émission carbone ?</t>
+  </si>
+  <si>
+    <t>Correct : le rapport indique une ambition zéro émission carbone d’ici 2035. Cela soutient l’ODD 13 avec une direction climatique claire. Chacun peut aider par une utilisation plus efficace de l’énergie et des ressources.</t>
+  </si>
+  <si>
+    <t>Quelles actions du rapport STOCKMEIER soutiennent directement l’action climatique ?</t>
+  </si>
+  <si>
+    <t>Comptabilité GES pour les scopes 1, 2 et 3.</t>
+  </si>
+  <si>
+    <t>Développement de l’énergie photovoltaïque chez STOCKMEIER Quimica.</t>
+  </si>
+  <si>
+    <t>Promotion de l’e-mobilité dans la flotte de l’entreprise.</t>
+  </si>
+  <si>
+    <t>Arrêter tout reporting de durabilité parce que c’est administratif.</t>
+  </si>
+  <si>
+    <t>Correct : la comptabilité GES, le photovoltaïque et l’e-mobilité soutiennent l’action climatique. Le reporting sert à la transparence et à l’amélioration. Chacun peut aider par de bonnes données, le signalement des problèmes et des déplacements efficaces.</t>
+  </si>
+  <si>
+    <t>Quelle est la différence entre atténuation et adaptation au changement climatique ?</t>
+  </si>
+  <si>
+    <t>L’atténuation concerne seulement les entreprises ; l’adaptation seulement les ménages.</t>
+  </si>
+  <si>
+    <t>L’atténuation réduit les causes ; l’adaptation prépare aux impacts.</t>
+  </si>
+  <si>
+    <t>L’atténuation signifie secours après une inondation ; l’adaptation signifie produire plus de CO2.</t>
+  </si>
+  <si>
+    <t>Il n’y a pas de différence.</t>
+  </si>
+  <si>
+    <t>Correct : l’atténuation agit sur les causes, l’adaptation prépare aux impacts. STOCKMEIER travaille sur les deux via la décarbonation et l’analyse des risques climatiques. Chacun peut réduire les émissions et suivre les procédures liées aux événements extrêmes.</t>
+  </si>
+  <si>
+    <t>Pourquoi l’éducation au climat fait-elle partie de l’ODD 13 ?</t>
+  </si>
+  <si>
+    <t>Parce que la connaissance seule résout automatiquement le changement climatique.</t>
+  </si>
+  <si>
+    <t>Parce que seuls les étudiants doivent comprendre le climat.</t>
+  </si>
+  <si>
+    <t>Parce que les personnes prennent de meilleures décisions lorsqu’elles comprennent les causes, impacts et solutions.</t>
+  </si>
+  <si>
+    <t>Parce que l’éducation remplace l’action pratique.</t>
+  </si>
+  <si>
+    <t>Correct : l’éducation aide à prendre de meilleures décisions. STOCKMEIER inclut des formations et actions de sensibilisation à la durabilité. Chacun peut poser des questions, partager des idées et transformer la connaissance en action.</t>
+  </si>
+  <si>
+    <t>Quel risque climatique le rapport STOCKMEIER mentionne-t-il explicitement pour les opérations et la chaîne d’approvisionnement ?</t>
+  </si>
+  <si>
+    <t>Les inondations, vagues de chaleur et perturbations logistiques peuvent affecter la production, le stockage et le transport.</t>
+  </si>
+  <si>
+    <t>Seulement trop d’arbres autour d’un site.</t>
+  </si>
+  <si>
+    <t>Seulement un manque de chaises de bureau.</t>
+  </si>
+  <si>
+    <t>Les risques climatiques existent seulement loin de l’Europe.</t>
+  </si>
+  <si>
+    <t>Correct : le rapport cite les inondations, fortes chaleurs et perturbations logistiques. STOCKMEIER prévoit une analyse des risques climatiques par site avant 2030. Chacun peut prendre au sérieux les alertes météo et procédures locales.</t>
+  </si>
+  <si>
+    <t>Quel choix quotidien réduit le plus clairement votre empreinte climatique personnelle ?</t>
+  </si>
+  <si>
+    <t>Acheter plus de produits parce que le neuf est toujours plus vert.</t>
+  </si>
+  <si>
+    <t>Laisser chauffage, lumières et équipements allumés car une personne ne change rien.</t>
+  </si>
+  <si>
+    <t>Prendre plus souvent l’avion mais recycler la carte d’embarquement.</t>
+  </si>
+  <si>
+    <t>Utiliser moins d’énergie, gaspiller moins, choisir un transport à plus faible impact et acheter seulement ce dont on a besoin.</t>
+  </si>
+  <si>
+    <t>Correct : les choix liés à l’énergie, au transport, aux déchets et à la consommation réduisent l’empreinte. STOCKMEIER travaille sur l’efficacité et les émissions ; chacun peut appliquer le même état d’esprit au travail et à la maison.</t>
+  </si>
+  <si>
+    <t>Quel est un bénéfice attendu du projet photovoltaïque de STOCKMEIER Quimica à L’Andana ?</t>
+  </si>
+  <si>
+    <t>Il rendra le reporting climatique inutile.</t>
+  </si>
+  <si>
+    <t>Il produira de l’électricité renouvelable et réduira la dépendance au réseau.</t>
+  </si>
+  <si>
+    <t>Il supprimera immédiatement toutes les émissions de Scope 3.</t>
+  </si>
+  <si>
+    <t>Il sert principalement à décorer les toits des entrepôts.</t>
+  </si>
+  <si>
+    <t>Correct : le projet PV doit produire de l’électricité renouvelable et réduire la dépendance au réseau. Cela soutient l’ambition Zero Carbon. Chacun peut éviter les consommations électriques inutiles.</t>
+  </si>
+  <si>
+    <t>Un plan climat est le plus solide lorsqu’il combine quels trois éléments ?</t>
+  </si>
+  <si>
+    <t>Mesure, actions pratiques et apprentissage.</t>
+  </si>
+  <si>
+    <t>Bonnes intentions, affiches et aucun suivi.</t>
+  </si>
+  <si>
+    <t>Un seul grand projet sans habitudes quotidiennes.</t>
+  </si>
+  <si>
+    <t>Attendre que quelqu’un d’autre commence.</t>
+  </si>
+  <si>
+    <t>Correct : l’action climatique nécessite mesure, actions concrètes et apprentissage. STOCKMEIER combine comptabilité GES, projets de décarbonation, risques climatiques et organisation durabilité. Chacun peut transformer la sensibilisation en actions répétées.</t>
+  </si>
+  <si>
+    <t>SDG 13 heißt Maßnahmen zum Klimaschutz. Was ist die Hauptidee dieses Ziels?</t>
   </si>
   <si>
     <t>Einfachauswahl</t>
   </si>
   <si>
-    <t>Nur große Projekte zählen, nicht kleine tägliche Entscheidungen.</t>
-  </si>
-  <si>
-    <t>Nachhaltigkeit ist ein fortlaufender Prozess, den wir jeden Tag unterstützen können.</t>
-  </si>
-  <si>
-    <t>Nachhaltigkeit betrifft nur Umweltabteilungen und Führungskräfte.</t>
-  </si>
-  <si>
-    <t>Nachhaltigkeit ist ein Thema für später, nicht für die heutige Arbeit.</t>
-  </si>
-  <si>
-    <t>Der Bericht beschreibt Nachhaltigkeit als einen täglichen Weg und nicht als einmaliges Ziel.</t>
-  </si>
-  <si>
-    <t>Welche Ziele passen zur Idee „Zero in Focus“?</t>
+    <t>Mehr Bäume zu pflanzen ist die einzige Klim Lösung.</t>
+  </si>
+  <si>
+    <t>Dringend Maßnahmen gegen den Klimawandel und seine Folgen ergreifen.</t>
+  </si>
+  <si>
+    <t>Warten, bis Klimawandel leichter zu messen ist.</t>
+  </si>
+  <si>
+    <t>Nur Regierungen müssen handeln; Unternehmen und Menschen spielen keine Rolle.</t>
+  </si>
+  <si>
+    <t>Richtig: SDG 13 verlangt dringende Maßnahmen gegen den Klimawandel und seine Folgen. STOCKMEIER verbindet dies mit Emissionsmessung, Klimarisiken und Dekarbonisierung. Du kannst durch emissionsärmere Entscheidungen helfen.</t>
+  </si>
+  <si>
+    <t>Welche drei Themen gehören zu den SDG-13-Zielvorgaben?</t>
   </si>
   <si>
     <t>Mehrfachauswahl</t>
   </si>
   <si>
-    <t>Null CO₂-Emissionen</t>
-  </si>
-  <si>
-    <t>Null Arbeitsunfälle</t>
-  </si>
-  <si>
-    <t>Null Toleranz gegenüber unethischem Verhalten</t>
-  </si>
-  <si>
-    <t>Null Schulungen</t>
-  </si>
-  <si>
-    <t>Die Idee verbindet Klima, Sicherheit und Integrität. Schulungen sind kein „Zero“-Ziel.</t>
+    <t>Widerstandsfähigkeit gegenüber klimabedingten Gefahren stärken.</t>
+  </si>
+  <si>
+    <t>Klimamaßnahmen in Politik und Planung integrieren.</t>
+  </si>
+  <si>
+    <t>Klimabildung und Bewusstsein verbessern.</t>
+  </si>
+  <si>
+    <t>Jedes Land muss exakt dieselbe Klimapolitik nutzen.</t>
+  </si>
+  <si>
+    <t>Richtig: Resilienz, Integration in Planung und Bildung. SDG 13 verlangt keine identische Politik für alle Länder. STOCKMEIER unterstützt dies durch Klimarisikoanalysen und Nachhaltigkeitswissen. Du kannst durch Lernen und Teilen konkreter Maßnahmen helfen.</t>
+  </si>
+  <si>
+    <t>Warum spricht SDG 13 von „Resilienz“ und nicht nur von „Emissionen senken“?</t>
+  </si>
+  <si>
+    <t>Weil Emissionsminderung nicht mehr sinnvoll ist.</t>
+  </si>
+  <si>
+    <t>Weil Klimarisiken nur Küstenländer betreffen.</t>
+  </si>
+  <si>
+    <t>Weil Gesellschaften sich auch auf Überschwemmungen, Hitzewellen und andere Klimafolgen vorbereiten müssen.</t>
+  </si>
+  <si>
+    <t>Weil Resilienz bedeutet, Klimawandel zu ignorieren.</t>
+  </si>
+  <si>
+    <t>Richtig: SDG 13 umfasst auch Anpassung an klimabedingte Gefahren. STOCKMEIER erkennt Risiken wie Überschwemmungen, Hitzewellen und Logistikstörungen. Du kannst helfen, indem du Sicherheits- und Notfallprozesse einhältst und Verbesserungen meldest.</t>
+  </si>
+  <si>
+    <t>Welche Scopes werden normalerweise genutzt, um den Klima-Fußabdruck eines Unternehmens zu verstehen?</t>
+  </si>
+  <si>
+    <t>Scope 1, Scope 2 und Scope 3.</t>
+  </si>
+  <si>
+    <t>Scope A, Scope B und Scope C.</t>
+  </si>
+  <si>
+    <t>Nur Stromverbrauch.</t>
+  </si>
+  <si>
+    <t>Nur Emissionen von Bürodruckern.</t>
+  </si>
+  <si>
+    <t>Richtig: Unternehmen nutzen üblicherweise Scope 1, 2 und 3. STOCKMEIER hat eine CO2-Bilanz nach GHG Protocol erstellt, inklusive wesentlicher Scope-3-Emissionen. Du kannst durch weniger Abfall, Energieverbrauch und unnötige Transporte helfen.</t>
+  </si>
+  <si>
+    <t>STOCKMEIER hat eine „Zero Carbon“-Ambition. Bis zu welchem Jahr strebt die Gruppe laut Bericht null CO2-Emissionen an?</t>
+  </si>
+  <si>
+    <t>Richtig: Der Bericht nennt das Ziel, bis 2035 null CO2-Emissionen anzustreben. Das unterstützt SDG 13 durch eine klare langfristige Richtung. Du kannst durch effizienteren Energie- und Ressourceneinsatz helfen.</t>
+  </si>
+  <si>
+    <t>Welche Maßnahmen aus dem STOCKMEIER-Bericht unterstützen den Klimaschutz direkt?</t>
+  </si>
+  <si>
+    <t>GHG-Bilanzierung für Scope 1, 2 und 3.</t>
+  </si>
+  <si>
+    <t>Ausbau von Photovoltaik bei STOCKMEIER Quimica.</t>
+  </si>
+  <si>
+    <t>Förderung von E-Mobilität in der Firmenflotte.</t>
+  </si>
+  <si>
+    <t>Alle Nachhaltigkeitsberichte stoppen, weil sie Papierarbeit sind.</t>
+  </si>
+  <si>
+    <t>Richtig: GHG-Bilanzierung, Photovoltaik und E-Mobilität unterstützen Klimaschutz. Reporting schafft Transparenz und Verbesserung. Du kannst mit guten Daten, Meldungen und effizienten Reisen helfen.</t>
+  </si>
+  <si>
+    <t>Was ist der Unterschied zwischen Klimaschutz und Klimaanpassung?</t>
+  </si>
+  <si>
+    <t>Klimaschutz ist nur für Unternehmen, Anpassung nur für Haushalte.</t>
+  </si>
+  <si>
+    <t>Klimaschutz verringert Ursachen; Anpassung bereitet auf Folgen vor.</t>
+  </si>
+  <si>
+    <t>Klimaschutz bedeutet Nothilfe nach einer Flut; Anpassung bedeutet mehr CO2 zu erzeugen.</t>
+  </si>
+  <si>
+    <t>Es gibt keinen Unterschied.</t>
+  </si>
+  <si>
+    <t>Richtig: Klimaschutz reduziert Ursachen, Anpassung bereitet auf Folgen vor. STOCKMEIER arbeitet an beidem durch Dekarbonisierung und Klimarisikoanalyse. Du kannst Emissionen senken und Verfahren bei Extremwetter beachten.</t>
+  </si>
+  <si>
+    <t>Warum ist Klimabildung Teil von SDG 13?</t>
+  </si>
+  <si>
+    <t>Weil Wissen allein den Klimawandel automatisch löst.</t>
+  </si>
+  <si>
+    <t>Weil nur Schülerinnen und Schüler Klimawandel verstehen müssen.</t>
+  </si>
+  <si>
+    <t>Weil Menschen bessere Entscheidungen treffen, wenn sie Ursachen, Folgen und Lösungen verstehen.</t>
+  </si>
+  <si>
+    <t>Weil Klimabildung praktische Maßnahmen ersetzt.</t>
+  </si>
+  <si>
+    <t>Richtig: Bildung hilft bei besseren Entscheidungen. STOCKMEIER nennt Nachhaltigkeitsschulungen und Sensibilisierung als Teil der Praxis. Du kannst Fragen stellen, Ideen teilen und Wissen in Handeln umsetzen.</t>
+  </si>
+  <si>
+    <t>Welches klimabezogene Risiko nennt der STOCKMEIER-Bericht ausdrücklich für Betrieb und Lieferketten?</t>
+  </si>
+  <si>
+    <t>Überschwemmungen, Hitzewellen und Logistikstörungen können Produktion, Lagerung und Transport betreffen.</t>
+  </si>
+  <si>
+    <t>Nur zu viele Bäume rund um einen Standort.</t>
+  </si>
+  <si>
+    <t>Nur ein Mangel an Bürostühlen.</t>
+  </si>
+  <si>
+    <t>Klimarisiken gibt es nur weit weg von Europa.</t>
+  </si>
+  <si>
+    <t>Richtig: Der Bericht nennt Überschwemmungen, extreme Hitze und Logistikstörungen. STOCKMEIER plant vor 2030 standortspezifische Klimarisikoanalysen. Du kannst Wetterwarnungen und Standortverfahren ernst nehmen.</t>
+  </si>
+  <si>
+    <t>Welche Alltagsentscheidung senkt deinen persönlichen Klima-Fußabdruck am deutlichsten?</t>
+  </si>
+  <si>
+    <t>Mehr Produkte kaufen, weil Neues immer grüner ist.</t>
+  </si>
+  <si>
+    <t>Heizung, Licht und Geräte anlassen, weil eine Person keinen Unterschied macht.</t>
+  </si>
+  <si>
+    <t>Öfter fliegen, aber die Bordkarte recyceln.</t>
+  </si>
+  <si>
+    <t>Weniger Energie nutzen, weniger verschwenden, emissionsärmeren Transport wählen und nur kaufen, was nötig ist.</t>
+  </si>
+  <si>
+    <t>Richtig: Entscheidungen zu Energie, Mobilität, Abfall und Konsum reduzieren den Fußabdruck. STOCKMEIER arbeitet an Effizienz und Emissionen; du kannst diese Denkweise im Alltag übernehmen.</t>
+  </si>
+  <si>
+    <t>Was ist ein erwarteter Nutzen des Photovoltaikprojekts bei STOCKMEIER Quimica in L’Andana?</t>
+  </si>
+  <si>
+    <t>Es macht Klimaberichterstattung überflüssig.</t>
+  </si>
+  <si>
+    <t>Es erzeugt erneuerbaren Strom und reduziert die Abhängigkeit vom Netzstrom.</t>
+  </si>
+  <si>
+    <t>Es beseitigt sofort alle Scope-3-Emissionen.</t>
+  </si>
+  <si>
+    <t>Es ist hauptsächlich Dekoration für Lagerdächer.</t>
+  </si>
+  <si>
+    <t>Richtig: Das PV-Projekt soll erneuerbaren Strom erzeugen und die Abhängigkeit vom Netzstrom senken. Das unterstützt Zero Carbon. Du kannst unnötigen Stromverbrauch vermeiden.</t>
+  </si>
+  <si>
+    <t>Ein Klimaplan ist am stärksten, wenn er welche drei Elemente kombiniert?</t>
+  </si>
+  <si>
+    <t>Messung, praktische Maßnahmen und Lernen.</t>
+  </si>
+  <si>
+    <t>Gute Absichten, Plakate und keine Nachverfolgung.</t>
+  </si>
+  <si>
+    <t>Nur ein großes Projekt und keine täglichen Gewohnheiten.</t>
+  </si>
+  <si>
+    <t>Warten, bis jemand anderes beginnt.</t>
+  </si>
+  <si>
+    <t>Richtig: Klimaschutz braucht Messung, praktische Maßnahmen und Lernen. STOCKMEIER kombiniert GHG-Bilanzierung, Dekarbonisierung, Klimarisiken und Nachhaltigkeitsorganisation. Du kannst Bewusstsein in kleine, wiederholbare Handlungen umsetzen.</t>
   </si>
   <si>
     <t>STOCKMEIER Sustainability Quiz - Questions Workbook</t>
   </si>
   <si>
-    <t>How to use this file</t>
-  </si>
-  <si>
-    <t>1. Keep this workbook named questions.xlsx and place it in the same folder as index.html.</t>
-  </si>
-  <si>
-    <t>2. Update the questions in the EN, NL, FR and DE sheets.</t>
-  </si>
-  <si>
-    <t>3. Keep the column names exactly as they are: type, question, note, option1, option2, option3, option4, correct, explanation.</t>
+    <t>Round content: SDG 13 - Climate Action</t>
+  </si>
+  <si>
+    <t>Balance: 7 SDG explanation questions, 4 STOCKMEIER action questions, 1 personal action question.</t>
+  </si>
+  <si>
+    <t>Keep column names exactly: type, question, note, option1, option2, option3, option4, correct, explanation.</t>
+  </si>
+  <si>
+    <t>Correct uses zero-based values: 0=option1, 1=option2, 2=option3, 3=option4. Multiple answers use commas.</t>
+  </si>
+  <si>
+    <t>Sources: STOCKMEIER Group Sustainability Report 2024/2025; https://sdgs.un.org/goals/goal13; https://sdgs.un.org/goals/goal13#targets_and_indicators; https://www.nationalgeographic.nl/226-manieren-om-onze-voetafdruk-te-verkleinen; https://www.wwf.nl/kom-in-actie/voetafdruktest; https://www.wwf.nl/work-in-progress/kom-in-actie/met-tijd/tips-gedrag/reizen</t>
   </si>
   <si>
     <t>4. The correct column uses zero-based values: 0 = option1, 1 = option2, 2 = option3, 3 = option4.</t>
@@ -396,53 +1174,19 @@
   </si>
   <si>
     <t>Created from the questions currently hardcoded in the provided index.html file.</t>
-  </si>
-  <si>
-    <t>Quels objectifs correspondent à l’idée « Zero in Focus » ?</t>
-  </si>
-  <si>
-    <t>Choix multiples</t>
-  </si>
-  <si>
-    <t>Zéro émission de CO₂</t>
-  </si>
-  <si>
-    <t>Zéro accident du travail</t>
-  </si>
-  <si>
-    <t>Tolérance zéro envers les comportements contraires à l’éthique</t>
-  </si>
-  <si>
-    <t>Zéro formation</t>
-  </si>
-  <si>
-    <t>Le concept « Zero in Focus » combine les objectifs liés au climat, à la sécurité et à l’intégrité. La formation n’est pas un objectif du programme « Zero ».</t>
-  </si>
-  <si>
-    <t>(Round 2) What does sustainability in everyday work mean most of all?</t>
-  </si>
-  <si>
-    <t>(Round 2) Which goals fit the “Zero in Focus” idea?</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -470,6 +1214,12 @@
       <name val="Aptos"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -480,7 +1230,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF2D3D3C"/>
+        <fgColor rgb="FF1F4E78"/>
       </patternFill>
     </fill>
   </fills>
@@ -507,26 +1257,30 @@
   </cellStyleXfs>
   <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Standaard" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -898,102 +1652,392 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:I13"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="12" customWidth="1"/>
+    <col min="1" max="1" width="11" customWidth="1"/>
     <col min="2" max="2" width="55" customWidth="1"/>
-    <col min="3" max="3" width="20" customWidth="1"/>
-    <col min="4" max="7" width="45" customWidth="1"/>
-    <col min="8" max="8" width="14" customWidth="1"/>
+    <col min="3" max="3" width="18" customWidth="1"/>
+    <col min="4" max="7" width="38" customWidth="1"/>
+    <col min="8" max="8" width="12" customWidth="1"/>
     <col min="9" max="9" width="65" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:9" ht="30" customHeight="1">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="5" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B2" s="2" t="s">
+    <row r="2" spans="1:9" ht="90" customHeight="1">
+      <c r="A2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="90" customHeight="1">
+      <c r="A3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="90" customHeight="1">
+      <c r="A4" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="90" customHeight="1">
+      <c r="A5" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="90" customHeight="1">
+      <c r="A6" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="I6" s="3" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="90" customHeight="1">
+      <c r="A7" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="I7" s="3" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="90" customHeight="1">
+      <c r="A8" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="90" customHeight="1">
+      <c r="A9" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="90" customHeight="1">
+      <c r="A10" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="I10" s="3" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="90" customHeight="1">
+      <c r="A11" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="F11" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="C2" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D2" s="2" t="s">
+      <c r="G11" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="I11" s="3" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="90" customHeight="1">
+      <c r="A12" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="C12" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="E2" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="I2" s="2" t="s">
+      <c r="D12" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="H12" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>24</v>
+      <c r="I12" s="3" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" ht="90" customHeight="1">
+      <c r="A13" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="I13" s="3" t="s">
+        <v>89</v>
       </c>
     </row>
   </sheetData>
@@ -1007,114 +2051,393 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:I4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:I13"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="12" customWidth="1"/>
+    <col min="1" max="1" width="11" customWidth="1"/>
     <col min="2" max="2" width="55" customWidth="1"/>
-    <col min="3" max="3" width="20" customWidth="1"/>
-    <col min="4" max="7" width="45" customWidth="1"/>
-    <col min="8" max="8" width="14" customWidth="1"/>
+    <col min="3" max="3" width="18" customWidth="1"/>
+    <col min="4" max="7" width="38" customWidth="1"/>
+    <col min="8" max="8" width="12" customWidth="1"/>
     <col min="9" max="9" width="65" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:9" ht="30" customHeight="1">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="5" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B2" s="2" t="s">
+    <row r="2" spans="1:9" ht="90" customHeight="1">
+      <c r="A2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="90" customHeight="1">
+      <c r="A3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="H3" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="C2" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B3" s="2" t="s">
+      <c r="I3" s="1" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="90" customHeight="1">
+      <c r="A4" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="F4" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="G4" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="H4" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="C3" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" s="4"/>
-      <c r="B4" s="6"/>
-      <c r="C4" s="2"/>
-      <c r="D4" s="7"/>
-      <c r="E4" s="7"/>
-      <c r="F4" s="7"/>
-      <c r="G4" s="7"/>
-      <c r="H4" s="4"/>
-      <c r="I4" s="7"/>
+      <c r="I4" s="7" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="90" customHeight="1">
+      <c r="A5" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="90" customHeight="1">
+      <c r="A6" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="I6" s="3" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="90" customHeight="1">
+      <c r="A7" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="I7" s="3" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="90" customHeight="1">
+      <c r="A8" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="90" customHeight="1">
+      <c r="A9" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="90" customHeight="1">
+      <c r="A10" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="I10" s="3" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="90" customHeight="1">
+      <c r="A11" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="I11" s="3" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="90" customHeight="1">
+      <c r="A12" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I12" s="3" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" ht="90" customHeight="1">
+      <c r="A13" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="I13" s="3" t="s">
+        <v>159</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1127,102 +2450,392 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:I3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:I13"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="12" customWidth="1"/>
+    <col min="1" max="1" width="11" customWidth="1"/>
     <col min="2" max="2" width="55" customWidth="1"/>
-    <col min="3" max="3" width="20" customWidth="1"/>
-    <col min="4" max="7" width="45" customWidth="1"/>
-    <col min="8" max="8" width="14" customWidth="1"/>
+    <col min="3" max="3" width="18" customWidth="1"/>
+    <col min="4" max="7" width="38" customWidth="1"/>
+    <col min="8" max="8" width="12" customWidth="1"/>
     <col min="9" max="9" width="65" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:9" ht="30" customHeight="1">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="5" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B2" s="2" t="s">
+    <row r="2" spans="1:9" ht="90" customHeight="1">
+      <c r="A2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="90" customHeight="1">
+      <c r="A3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="90" customHeight="1">
+      <c r="A4" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="90" customHeight="1">
+      <c r="A5" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="H5" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C2" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="E2" s="2" t="s">
+      <c r="I5" s="3" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="90" customHeight="1">
+      <c r="A6" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="D6" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="E6" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="F6" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="H2" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="I2" s="2" t="s">
+      <c r="G6" s="3" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="3" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>74</v>
+      <c r="H6" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="I6" s="3" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="90" customHeight="1">
+      <c r="A7" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="I7" s="3" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="90" customHeight="1">
+      <c r="A8" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="90" customHeight="1">
+      <c r="A9" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="90" customHeight="1">
+      <c r="A10" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="I10" s="3" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="90" customHeight="1">
+      <c r="A11" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="I11" s="3" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="90" customHeight="1">
+      <c r="A12" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I12" s="3" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" ht="90" customHeight="1">
+      <c r="A13" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="I13" s="3" t="s">
+        <v>229</v>
       </c>
     </row>
   </sheetData>
@@ -1236,102 +2849,392 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:I3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:I13"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="12" customWidth="1"/>
+    <col min="1" max="1" width="11" customWidth="1"/>
     <col min="2" max="2" width="55" customWidth="1"/>
-    <col min="3" max="3" width="20" customWidth="1"/>
-    <col min="4" max="7" width="45" customWidth="1"/>
-    <col min="8" max="8" width="14" customWidth="1"/>
+    <col min="3" max="3" width="18" customWidth="1"/>
+    <col min="4" max="7" width="38" customWidth="1"/>
+    <col min="8" max="8" width="12" customWidth="1"/>
     <col min="9" max="9" width="65" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:9" ht="30" customHeight="1">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="5" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B2" s="2" t="s">
+    <row r="2" spans="1:9" ht="90" customHeight="1">
+      <c r="A2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="90" customHeight="1">
+      <c r="A3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="90" customHeight="1">
+      <c r="A4" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="90" customHeight="1">
+      <c r="A5" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="90" customHeight="1">
+      <c r="A6" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="H6" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="C2" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>59</v>
+      <c r="I6" s="3" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="90" customHeight="1">
+      <c r="A7" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>258</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="I7" s="3" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="90" customHeight="1">
+      <c r="A8" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="90" customHeight="1">
+      <c r="A9" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>270</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>273</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>274</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="90" customHeight="1">
+      <c r="A10" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="I10" s="3" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="90" customHeight="1">
+      <c r="A11" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>286</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="I11" s="3" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="90" customHeight="1">
+      <c r="A12" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>289</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>291</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>292</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I12" s="3" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" ht="90" customHeight="1">
+      <c r="A13" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>294</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>295</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>296</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>297</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>298</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="I13" s="3" t="s">
+        <v>299</v>
       </c>
     </row>
   </sheetData>
@@ -1346,55 +3249,57 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:A10"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="120" customWidth="1"/>
+    <col min="1" max="1" width="130" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="21" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" s="4"/>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A3" s="5" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A4" s="4" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A6" s="4" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A7" s="4" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A8" s="4" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A9" s="4"/>
-    </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A10" s="4" t="s">
-        <v>67</v>
+    <row r="1" spans="1:1" ht="35.1" customHeight="1">
+      <c r="A1" s="2" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" ht="35.1" customHeight="1">
+      <c r="A2" s="3" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" ht="35.1" customHeight="1">
+      <c r="A3" s="4" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" ht="35.1" customHeight="1">
+      <c r="A4" s="3" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" ht="35.1" customHeight="1">
+      <c r="A5" s="3" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" ht="35.1" customHeight="1">
+      <c r="A6" s="3" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1">
+      <c r="A7" s="3" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" s="3" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9" s="3"/>
+    </row>
+    <row r="10" spans="1:1">
+      <c r="A10" s="3" t="s">
+        <v>308</v>
       </c>
     </row>
   </sheetData>
